--- a/secondary_acs_v2/conf/definitions.xlsx
+++ b/secondary_acs_v2/conf/definitions.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28730"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\mike\Desktop\2_responsibilities\nvi_etl\secondary_acs_v2\conf\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{87DB8DB1-CBD9-422B-8653-183D705E4E96}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0D5A58A9-9A68-4CF7-B187-00A1D5BC9DEF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3420" yWindow="240" windowWidth="20780" windowHeight="14350" xr2:uid="{2AB755C4-24C8-4837-A10C-3A711D659246}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="16220" activeTab="2" xr2:uid="{2AB755C4-24C8-4837-A10C-3A711D659246}"/>
   </bookViews>
   <sheets>
     <sheet name="About" sheetId="7" r:id="rId1"/>
@@ -62,7 +62,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="98" uniqueCount="74">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="99" uniqueCount="74">
   <si>
     <t>name</t>
   </si>
@@ -1223,7 +1223,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6BFCD738-91A8-4D6B-8700-399E55C1853B}">
-  <dimension ref="A1:B2"/>
+  <dimension ref="A1:B3"/>
   <sheetFormatPr defaultColWidth="25.453125" defaultRowHeight="15.5" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="23.54296875" style="1" customWidth="1"/>
@@ -1243,6 +1243,14 @@
         <v>2023</v>
       </c>
       <c r="B2" s="8" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A3" s="1">
+        <v>2024</v>
+      </c>
+      <c r="B3" s="2" t="s">
         <v>25</v>
       </c>
     </row>
